--- a/public/DataMahasiswa/mahasiswa.xlsx
+++ b/public/DataMahasiswa/mahasiswa.xlsx
@@ -1,65 +1,187 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27726"/>
-  <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp_oh\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F67BE297-112E-4F51-97BD-9B06F190B8B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="5652" yWindow="2724" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" forceFullCalc="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>Teknik Informatika</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="49">
+  <si>
+    <t>Nama Mahasiswa</t>
+  </si>
+  <si>
+    <t>No Telp</t>
+  </si>
+  <si>
+    <t>Prodi</t>
+  </si>
+  <si>
+    <t>Kelompok</t>
+  </si>
+  <si>
+    <t>Ahmad</t>
+  </si>
+  <si>
+    <t>Budi</t>
+  </si>
+  <si>
+    <t>Citra</t>
+  </si>
+  <si>
+    <t>Dewi</t>
+  </si>
+  <si>
+    <t>Eka</t>
+  </si>
+  <si>
+    <t>Fajar</t>
+  </si>
+  <si>
+    <t>Gita</t>
+  </si>
+  <si>
+    <t>Hadi</t>
+  </si>
+  <si>
+    <t>Indah</t>
+  </si>
+  <si>
+    <t>Joko</t>
+  </si>
+  <si>
+    <t>Kiki</t>
+  </si>
+  <si>
+    <t>Lina</t>
+  </si>
+  <si>
+    <t>Maya</t>
+  </si>
+  <si>
+    <t>Nina</t>
+  </si>
+  <si>
+    <t>Omar</t>
+  </si>
+  <si>
+    <t>Putri</t>
+  </si>
+  <si>
+    <t>Rina</t>
+  </si>
+  <si>
+    <t>Sinta</t>
+  </si>
+  <si>
+    <t>Teguh</t>
+  </si>
+  <si>
+    <t>Umar</t>
+  </si>
+  <si>
+    <t>Vina</t>
+  </si>
+  <si>
+    <t>Wawan</t>
+  </si>
+  <si>
+    <t>Xenia</t>
+  </si>
+  <si>
+    <t>Yudi</t>
+  </si>
+  <si>
+    <t>Zara</t>
+  </si>
+  <si>
+    <t>08111111111</t>
+  </si>
+  <si>
+    <t>08222222222</t>
+  </si>
+  <si>
+    <t>08333333333</t>
+  </si>
+  <si>
+    <t>08444444444</t>
+  </si>
+  <si>
+    <t>08555555555</t>
+  </si>
+  <si>
+    <t>08666666666</t>
+  </si>
+  <si>
+    <t>08777777777</t>
+  </si>
+  <si>
+    <t>08888888888</t>
+  </si>
+  <si>
+    <t>08999999999</t>
+  </si>
+  <si>
+    <t>08000000000</t>
+  </si>
+  <si>
+    <t>Prodi A</t>
+  </si>
+  <si>
+    <t>Prodi B</t>
+  </si>
+  <si>
+    <t>Prodi C</t>
+  </si>
+  <si>
+    <t>Prodi D</t>
+  </si>
+  <si>
+    <t>Prodi E</t>
   </si>
   <si>
     <t>Kelompok 1</t>
   </si>
   <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>Sistem Informasi</t>
-  </si>
-  <si>
     <t>Kelompok 2</t>
+  </si>
+  <si>
+    <t>Kelompok 3</t>
+  </si>
+  <si>
+    <t>Kelompok 4</t>
+  </si>
+  <si>
+    <t>Kelompok 5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -70,7 +192,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -78,26 +200,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -176,7 +308,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -211,7 +342,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -387,40 +517,372 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
